--- a/jogos_2025-02-05.xlsx
+++ b/jogos_2025-02-05.xlsx
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Cape Town City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
         <v>5</v>
       </c>
-      <c r="P7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="T7" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W7" t="n">
         <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.37</v>
+        <v>2.52</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.17</v>
       </c>
-      <c r="AC7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['5', '47']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>1.98</v>
       </c>
       <c r="AI7" t="n">
-        <v>3</v>
+        <v>1.58</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.62</v>
+        <v>2.87</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45693.60416666666</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['5', '47']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.62</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45693.60416666666</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cape Town City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.37</v>
       </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="AD10" t="n">
         <v>1.5</v>
       </c>
-      <c r="X10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45693.60416666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.7</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.93</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.56</v>
       </c>
-      <c r="O11" t="n">
-        <v>6</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['7', '35']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['15', '25']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AI11" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>2.35</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45693.64583333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2.05</v>
       </c>
-      <c r="M12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.9</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['7', '35']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '25']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.56</v>
+        <v>1.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45693.64583333334</v>
@@ -2062,109 +2062,109 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['76', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="N13" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['5', '9', '66', '72', '76', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>3.5</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45693.6875</v>
@@ -2191,109 +2191,109 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.44</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
-        <v>3.47</v>
+        <v>5.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2.68</v>
+        <v>8.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9</v>
+        <v>1.71</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>6.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.05</v>
+        <v>2.82</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.7</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['76', '90+4']</t>
+          <t>['5', '9', '66', '72', '76', '90+2']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.52</v>
+        <v>3.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.9</v>
+        <v>1.31</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45693.6875</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,109 +2320,109 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.13</v>
+        <v>4.5</v>
       </c>
       <c r="M15" t="n">
-        <v>7.6</v>
+        <v>3.61</v>
       </c>
       <c r="N15" t="n">
-        <v>17</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.38</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X15" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q15" t="n">
-        <v>11</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X15" t="n">
-        <v>9.5</v>
-      </c>
       <c r="Y15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['17', '26']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['18', '45+1', '55', '59', '71', '81']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>7</v>
-      </c>
       <c r="AI15" t="n">
-        <v>1.15</v>
+        <v>2.62</v>
       </c>
       <c r="AJ15" t="n">
-        <v>5.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45693.69791666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.5</v>
+        <v>1.13</v>
       </c>
       <c r="M16" t="n">
-        <v>3.61</v>
+        <v>7.6</v>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>17</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="S16" t="n">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.05</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.32</v>
-      </c>
       <c r="X16" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.87</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.87</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
+          <t>['18', '45+1', '55', '59', '71', '81']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['17', '26']</t>
-        </is>
-      </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>7</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.62</v>
+        <v>5.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45693.69791666666</v>
